--- a/graphy/results/graphy_20260512_은행조회서완전성.xlsx
+++ b/graphy/results/graphy_20260512_은행조회서완전성.xlsx
@@ -1,29 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <calcPr calcId="171027"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="은행조회서완전성" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -38,22 +56,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -132,7 +213,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -167,7 +247,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -202,16 +281,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -333,46 +416,2623 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>적요란</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(5.03%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>1278227</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(5.03%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>2556454</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원금상환(4.97%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>20381</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 이자상환(4.97%)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>33489685</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.29%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>8973081</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(5.57%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>9758531</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.901%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2929011</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(5.03%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v>1281616</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(5.03%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>2563232</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.42%)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>33473393</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.29%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>8985753</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(5.57%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>9745210</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.901%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2930561</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.57%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>1150027</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.57%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>2300054</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.58%)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="n">
+        <v>27914785</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.29%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>8116164</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(5.57%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" s="2" t="n">
+        <v>8780761</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.311%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2420657</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R25년도 1분기 감사수정_CPS 보통주 전환 상각 (보통주 전환 전)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="2" t="n">
+        <v>5272275</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25년도 1분기 감사수정_RCPS 미전환주식 상각</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>28375</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25년도 1분기 감사수정_차입금 미지급비용 반영_수정</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" s="2" t="n">
+        <v>1542880</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.57%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" s="2" t="n">
+        <v>1164410</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.57%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="2" t="n">
+        <v>2328821</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.58%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" s="2" t="n">
+        <v>30885512</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" s="2" t="n">
+        <v>8509041</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(5.03%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
+        <v>8758401</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.311%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>2680013</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.57%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" s="2" t="n">
+        <v>1126849</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.57%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" s="2" t="n">
+        <v>2253698</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.27%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v>29802990</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" s="2" t="n">
+        <v>8219178</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(5.03%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
+        <v>8454534</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" s="2" t="n">
+        <v>47945</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.311%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>2593561</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.44%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" s="2" t="n">
+        <v>1161205</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" s="2" t="n">
+        <v>2322410</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.27%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" s="2" t="n">
+        <v>28758742</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" s="2" t="n">
+        <v>8280821</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(5.03%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" s="2" t="n">
+        <v>8714991</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.131%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>2519589</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RCPS 미전환주식 상각</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" s="2" t="n">
+        <v>42311</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6월 퇴직급여 미지급 기간이자 적용</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>전사임직원</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" s="2" t="n">
+        <v>111668182</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.44%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" s="2" t="n">
+        <v>1094794</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" s="2" t="n">
+        <v>2189589</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.27%)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" s="2" t="n">
+        <v>27813493</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" s="2" t="n">
+        <v>8013698</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.75%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" s="2" t="n">
+        <v>7945513</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.131%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>2604835</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>차입금 이자(25.07.01~25.07.31 / 4.6%)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>조건호</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" s="2" t="n">
+        <v>2734794</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.44%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" s="2" t="n">
+        <v>1131287</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" s="2" t="n">
+        <v>2262575</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.07%)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" s="2" t="n">
+        <v>28680194</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" s="2" t="n">
+        <v>8280821</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.75%) 원리금상환</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" s="2" t="n">
+        <v>8189520</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>하나은행 신성장일자리 시설대출 / 5억(6.131%) 이자</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>하나B(42142)시설5억대출</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" s="2" t="n">
+        <v>2099657</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>우리은행 기업운전일반자금대출-IP담보 / 20억(5.00%) 이자</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>우리(5208)-IP대출20억</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" s="2" t="n">
+        <v>1602739</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>차입금 이자(25.08.01~25.08.31 / 4.6%)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>조건호</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" s="2" t="n">
+        <v>2734794</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.44%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" s="2" t="n">
+        <v>1127835</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" s="2" t="n">
+        <v>2255670</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.07%)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="2" t="n">
+        <v>27359878</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.44%) 원금상환</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" s="2" t="n">
+        <v>21475</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="2" t="n">
+        <v>8149178</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>차입금 이자(25.09.01~25.09.30 / 4.6%)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>조건호</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" s="2" t="n">
+        <v>2646575</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>단기차입금 이자(2025/07/20~2025/09/08_4.6%)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>박성현</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" s="2" t="n">
+        <v>2205479</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>미전환 RCPS 상각분 회계처리</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.30%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" s="2" t="n">
+        <v>1060273</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.30%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" s="2" t="n">
+        <v>2120547</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(4.07%)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" s="2" t="n">
+        <v>26461132</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" s="2" t="n">
+        <v>7407035</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>하나카드 결제</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>하나(6771)-법인명의</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" s="2" t="n">
+        <v>11454</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.30%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" s="2" t="n">
+        <v>1095616</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.30%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" s="2" t="n">
+        <v>2191232</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 대출연장 및 원금상환(3.88%)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" s="2" t="n">
+        <v>15053</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 이자상환(4.19%)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" s="2" t="n">
+        <v>27333999</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" s="2" t="n">
+        <v>7598482</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리은행 신용보증기금대출 / 3억(4.57%) 이자상환 </t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" s="2" t="n">
+        <v>1064712</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>우리은행 신용보증기금대출 / 6억(4.57%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" s="2" t="n">
+        <v>2129424</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>우리은행 시설자금 부동산 담보 / 82억 원리금상환(3.88%)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>우리CUBE론(82억)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" s="2" t="n">
+        <v>25260519</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>하나은행 당좌계좌 대출이자</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>311182</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>우리은행 운전자금 부동산 담보 / 22억(4.44%) 이자상환</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>우리_CUBE론_22억</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" s="2" t="n">
+        <v>7336339</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2025년 4분기 차입금 미지급비용 반영</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" s="2" t="n">
+        <v>332227</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>25년 퇴직급여 미지급이자 결산</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>전사임직원</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" s="2" t="n">
+        <v>75430716</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>RCPS 미전환주식 상각</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" s="2" t="n">
+        <v>49598</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>당좌예금 12월분 이자결산 (미지급비용)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" s="2" t="n">
+        <v>1859616</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>조건호 차입금 입금(25.07.01~25.09.26 / 4.6%)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>조건호</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>700000000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>단기차입금 - 수정예정</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>우리7396-주계좌</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>350000000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>25년 4분기 당좌예금 → 단기차입금 계정대체</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>하나B7404-주계좌</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>102-85-02451</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>1956056895</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>